--- a/extenbooks/XS1201.xlsx
+++ b/extenbooks/XS1201.xlsx
@@ -483,7 +483,7 @@
         <v>1952</v>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.0259143411707378</v>
+        <v>-0.0374161882283763</v>
       </c>
     </row>
     <row r="4">
@@ -491,7 +491,7 @@
         <v>1953</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.0237632894675991</v>
+        <v>-0.0324373487351561</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         <v>1954</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.0175230252797984</v>
+        <v>-0.0214436600785048</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>1955</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-0.0231196442589276</v>
+        <v>-0.0265489637537075</v>
       </c>
     </row>
     <row r="7">
@@ -515,7 +515,7 @@
         <v>1956</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>-0.0301420041704406</v>
+        <v>-0.0272324875988365</v>
       </c>
     </row>
     <row r="8">
@@ -523,7 +523,7 @@
         <v>1957</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-0.027606167425043</v>
+        <v>-0.0217501091682329</v>
       </c>
     </row>
     <row r="9">
@@ -531,7 +531,7 @@
         <v>1958</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>-0.0146801211065833</v>
+        <v>-0.0107956918639566</v>
       </c>
     </row>
     <row r="10">
@@ -539,7 +539,7 @@
         <v>1959</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-0.0259817810272709</v>
+        <v>-0.0161739390477212</v>
       </c>
     </row>
     <row r="11">
@@ -547,7 +547,7 @@
         <v>1960</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.0351053316666113</v>
+        <v>-0.0218783071709606</v>
       </c>
     </row>
     <row r="12">
@@ -555,7 +555,7 @@
         <v>1961</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-0.0284682386799215</v>
+        <v>-0.0108699789580031</v>
       </c>
     </row>
     <row r="13">
@@ -563,7 +563,7 @@
         <v>1962</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>-0.0322715516242163</v>
+        <v>-0.0162646831875639</v>
       </c>
     </row>
     <row r="14">
@@ -571,7 +571,7 @@
         <v>1963</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>-0.0353679504274845</v>
+        <v>-0.0216813867754333</v>
       </c>
     </row>
     <row r="15">
@@ -579,7 +579,7 @@
         <v>1964</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-0.0300657452590363</v>
+        <v>-0.0118341466265377</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         <v>1965</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-0.0290237360381199</v>
+        <v>-0.0107726236007808</v>
       </c>
     </row>
     <row r="17">
@@ -595,7 +595,7 @@
         <v>1966</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.0327004452837054</v>
+        <v>-0.016336699392929</v>
       </c>
     </row>
     <row r="18">
@@ -603,7 +603,7 @@
         <v>1967</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-0.0255499390087201</v>
+        <v>-0.0110591318888458</v>
       </c>
     </row>
     <row r="19">
@@ -611,7 +611,7 @@
         <v>1968</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-0.0280346270827331</v>
+        <v>-0.0167347932442531</v>
       </c>
     </row>
     <row r="20">
@@ -619,7 +619,7 @@
         <v>1969</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>-0.0367519150169759</v>
+        <v>-0.0284179183679485</v>
       </c>
     </row>
     <row r="21">
@@ -627,7 +627,7 @@
         <v>1970</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>-0.0220645987200259</v>
+        <v>-0.0115212572777677</v>
       </c>
     </row>
     <row r="22">
@@ -635,7 +635,7 @@
         <v>1971</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-0.009947632742413099</v>
+        <v>0.0056605571532815</v>
       </c>
     </row>
     <row r="23">
@@ -643,7 +643,7 @@
         <v>1972</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-0.0175187435013407</v>
+        <v>-0.0056776977742336</v>
       </c>
     </row>
     <row r="24">
@@ -651,7 +651,7 @@
         <v>1973</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>-0.0211618548368991</v>
+        <v>-0.005702565498507</v>
       </c>
     </row>
     <row r="25">
@@ -659,7 +659,7 @@
         <v>1974</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-0.0153194675529997</v>
+        <v>-0.0057679601201882</v>
       </c>
     </row>
     <row r="26">
@@ -667,7 +667,7 @@
         <v>1975</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.0116643440813245</v>
+        <v>0.0225218766173028</v>
       </c>
     </row>
     <row r="27">
@@ -675,7 +675,7 @@
         <v>1976</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.0026306012772417</v>
+        <v>0.011293298003856</v>
       </c>
     </row>
     <row r="28">
@@ -683,7 +683,7 @@
         <v>1977</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>-0.0044159790491616</v>
+        <v>0.0056518652375366</v>
       </c>
     </row>
     <row r="29">
@@ -691,7 +691,7 @@
         <v>1978</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.011542826816987</v>
+        <v>-0.0056524517998179</v>
       </c>
     </row>
     <row r="30">
@@ -699,7 +699,7 @@
         <v>1979</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-0.0151414000433138</v>
+        <v>-0.0113529575428771</v>
       </c>
     </row>
     <row r="31">
@@ -707,7 +707,7 @@
         <v>1980</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0.006461748772533</v>
+        <v>-0.0057334406138367</v>
       </c>
     </row>
     <row r="32">
@@ -715,7 +715,7 @@
         <v>1981</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-0.0130900415679126</v>
+        <v>-0.005635755826009</v>
       </c>
     </row>
     <row r="33">
@@ -723,7 +723,7 @@
         <v>1982</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>-0.0019516183586942</v>
+        <v>-0.0057031409577578</v>
       </c>
     </row>
     <row r="34">
@@ -731,7 +731,7 @@
         <v>1983</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.0024743549737234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -739,7 +739,7 @@
         <v>1984</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-0.0070468863657809</v>
+        <v>-0.0109665289863094</v>
       </c>
     </row>
     <row r="36">
@@ -747,7 +747,7 @@
         <v>1985</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-0.009857733812493601</v>
+        <v>-0.0163694039542482</v>
       </c>
     </row>
     <row r="37">
@@ -755,7 +755,7 @@
         <v>1986</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-0.009019023585087899</v>
+        <v>-0.0109676958689466</v>
       </c>
     </row>
     <row r="38">
@@ -763,7 +763,7 @@
         <v>1987</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>-0.0157820199517426</v>
+        <v>-0.016617595719242</v>
       </c>
     </row>
     <row r="39">
@@ -771,7 +771,7 @@
         <v>1988</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>-0.018006935248732</v>
+        <v>-0.016643565721584</v>
       </c>
     </row>
     <row r="40">
@@ -779,7 +779,7 @@
         <v>1989</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-0.0179056753604486</v>
+        <v>-0.0218307637222196</v>
       </c>
     </row>
     <row r="41">
@@ -1809,7 +1809,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"1964": -0.0167, "1997": 0.006, "2010": 0.086}</t>
+          <t>{"1964": -0.005, "1975": 0.028, "1997": 0.003, "2010": 0.086}</t>
         </is>
       </c>
     </row>
